--- a/data/food.xlsx
+++ b/data/food.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\R\PycharmProjects\kr\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\R\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB03C017-B7FF-47C8-B115-78945818A16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB31E86F-FFC0-471B-A9AD-0FB381D9C490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8490" yWindow="3135" windowWidth="28800" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="4215" windowWidth="28800" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>date</t>
   </si>
   <si>
     <t>category</t>
+  </si>
+  <si>
+    <t>food</t>
   </si>
   <si>
     <t>Молочные продукты</t>
@@ -93,7 +96,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -103,12 +106,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -125,19 +122,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,102 +413,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
     <col min="3" max="3" width="47.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>45788</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>45758</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4">
-        <v>1</v>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>15655</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>45787</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="2">
+        <v>45726</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4">
-        <v>5</v>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>45786</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4">
-        <v>9</v>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>458484</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>45785</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="2">
+        <v>45755</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4">
-        <v>2</v>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>448441</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45784</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="4">
-        <v>6</v>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>15872</v>
       </c>
     </row>
   </sheetData>
